--- a/data/trans_dic/P21D_2_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P21D_2_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,44</t>
+          <t>0,0; 0,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 7,37</t>
+          <t>0,12; 7,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 3,02</t>
+          <t>0,11; 3,04</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,58</t>
+          <t>0,28; 3,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,68</t>
+          <t>0,36; 2,67</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,97</t>
+          <t>0,46; 3,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,37</t>
+          <t>1,21; 4,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,35</t>
+          <t>1,04; 3,32</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,03</t>
+          <t>0,31; 3,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 10,9</t>
+          <t>1,13; 10,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,56</t>
+          <t>0,77; 4,51</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,25</t>
+          <t>2,05; 6,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,38</t>
+          <t>2,42; 6,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,97</t>
+          <t>2,81; 5,87</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,24</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,73</t>
+          <t>0,31; 2,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,4</t>
+          <t>0,43; 2,39</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,86</t>
+          <t>0,33; 2,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,61</t>
+          <t>0,19; 1,85</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,26</t>
+          <t>0,87; 2,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,58</t>
+          <t>1,65; 3,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,53</t>
+          <t>1,37; 2,59</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 889</t>
+          <t>0; 868</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>172; 10340</t>
+          <t>175; 10737</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>403; 10399</t>
+          <t>372; 10476</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8704</t>
+          <t>0; 7891</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1001; 10353</t>
+          <t>807; 10530</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1861; 13251</t>
+          <t>1770; 13210</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>814; 8564</t>
+          <t>999; 8339</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2735; 11250</t>
+          <t>3113; 11810</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5393; 15840</t>
+          <t>4935; 15712</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1907; 21241</t>
+          <t>1628; 20389</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3910; 34977</t>
+          <t>3632; 33236</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6575; 38609</t>
+          <t>6538; 38240</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5061; 17288</t>
+          <t>4900; 15980</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5489; 14502</t>
+          <t>5511; 14556</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12706; 27815</t>
+          <t>13078; 27356</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6623</t>
+          <t>0; 5220</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>576; 5072</t>
+          <t>575; 5391</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1526; 8203</t>
+          <t>1471; 8166</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1175</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>565; 4874</t>
+          <t>559; 4862</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>552; 4650</t>
+          <t>557; 5345</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>15063; 37634</t>
+          <t>14538; 37524</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>25945; 56964</t>
+          <t>26281; 59403</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45105; 82350</t>
+          <t>44458; 84305</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_2_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P21D_2_R-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 5,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 7,65</t>
+          <t>0,74; 9,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,04</t>
+          <t>0,62; 5,2</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 4,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,64</t>
+          <t>0,86; 4,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,67</t>
+          <t>0,76; 3,31</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,87</t>
+          <t>1,07; 5,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,58</t>
+          <t>1,18; 4,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,32</t>
+          <t>1,46; 3,96</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,87</t>
+          <t>1,69; 6,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,36</t>
+          <t>0,94; 3,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,51</t>
+          <t>1,64; 3,94</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,7</t>
+          <t>1,88; 6,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,4</t>
+          <t>2,85; 7,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,87</t>
+          <t>2,76; 5,77</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,9</t>
+          <t>0,34; 2,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,39</t>
+          <t>0,49; 2,35</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,85</t>
+          <t>0,3; 2,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,85</t>
+          <t>0,18; 1,68</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,26</t>
+          <t>1,54; 3,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,73</t>
+          <t>1,81; 3,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,59</t>
+          <t>1,85; 2,82</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>7779</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 868</t>
+          <t>0; 11811</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>175; 10737</t>
+          <t>1207; 14788</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>372; 10476</t>
+          <t>2311; 19450</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>8026</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7891</t>
+          <t>0; 9336</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>807; 10530</t>
+          <t>2136; 11697</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1770; 13210</t>
+          <t>3605; 15755</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>13676</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>999; 8339</t>
+          <t>2692; 13738</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3113; 11810</t>
+          <t>3498; 12711</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4935; 15712</t>
+          <t>8033; 21768</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19346</t>
+          <t>17109</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1628; 20389</t>
+          <t>5369; 19131</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3632; 33236</t>
+          <t>3250; 11515</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6538; 38240</t>
+          <t>10890; 26086</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>21289</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4900; 15980</t>
+          <t>4828; 16650</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5511; 14556</t>
+          <t>7256; 17836</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13078; 27356</t>
+          <t>14115; 29535</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4159</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5220</t>
+          <t>0; 5792</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>575; 5391</t>
+          <t>684; 5928</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1471; 8166</t>
+          <t>1843; 8796</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2059</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>559; 4862</t>
+          <t>567; 5152</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>557; 5345</t>
+          <t>567; 5328</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>74096</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14538; 37524</t>
+          <t>24192; 48147</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>26281; 59403</t>
+          <t>30641; 54152</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>44458; 84305</t>
+          <t>60451; 91886</t>
         </is>
       </c>
     </row>
